--- a/data/result/Sarah McLachlan/2025-04-26.xlsx
+++ b/data/result/Sarah McLachlan/2025-04-26.xlsx
@@ -9675,7 +9675,7 @@
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>472.43</v>
+        <v>357</v>
       </c>
       <c r="B206" t="s">
         <v>207</v>
@@ -14407,7 +14407,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="785" spans="1:3">
+    <row r="785" spans="2:3">
       <c r="B785" t="s">
         <v>786</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="786" spans="1:3">
+    <row r="786" spans="2:3">
       <c r="B786" t="s">
         <v>787</v>
       </c>
@@ -14423,7 +14423,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="787" spans="1:3">
+    <row r="787" spans="2:3">
       <c r="B787" t="s">
         <v>788</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="788" spans="1:3">
+    <row r="788" spans="2:3">
       <c r="B788" t="s">
         <v>789</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="789" spans="1:3">
+    <row r="789" spans="2:3">
       <c r="B789" t="s">
         <v>790</v>
       </c>
@@ -14447,7 +14447,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="790" spans="1:3">
+    <row r="790" spans="2:3">
       <c r="B790" t="s">
         <v>791</v>
       </c>
@@ -14455,7 +14455,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="791" spans="1:3">
+    <row r="791" spans="2:3">
       <c r="B791" t="s">
         <v>792</v>
       </c>
@@ -14463,7 +14463,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="792" spans="1:3">
+    <row r="792" spans="2:3">
       <c r="B792" t="s">
         <v>793</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="793" spans="1:3">
+    <row r="793" spans="2:3">
       <c r="B793" t="s">
         <v>794</v>
       </c>
@@ -14479,7 +14479,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="794" spans="1:3">
+    <row r="794" spans="2:3">
       <c r="B794" t="s">
         <v>795</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="795" spans="1:3">
+    <row r="795" spans="2:3">
       <c r="B795" t="s">
         <v>796</v>
       </c>
@@ -14495,7 +14495,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="796" spans="1:3">
+    <row r="796" spans="2:3">
       <c r="B796" t="s">
         <v>797</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="797" spans="1:3">
+    <row r="797" spans="2:3">
       <c r="B797" t="s">
         <v>798</v>
       </c>
@@ -14511,7 +14511,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="798" spans="1:3">
+    <row r="798" spans="2:3">
       <c r="B798" t="s">
         <v>799</v>
       </c>
@@ -14519,7 +14519,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="799" spans="1:3">
+    <row r="799" spans="2:3">
       <c r="B799" t="s">
         <v>800</v>
       </c>
@@ -14527,29 +14527,23 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="800" spans="1:3">
-      <c r="A800">
-        <v>428.4</v>
-      </c>
+    <row r="800" spans="2:3">
       <c r="B800" t="s">
         <v>801</v>
       </c>
       <c r="C800" t="s">
-        <v>2538</v>
-      </c>
-    </row>
-    <row r="801" spans="1:3">
-      <c r="A801">
-        <v>428.4</v>
-      </c>
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="801" spans="2:3">
       <c r="B801" t="s">
         <v>802</v>
       </c>
       <c r="C801" t="s">
-        <v>2538</v>
-      </c>
-    </row>
-    <row r="802" spans="1:3">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="802" spans="2:3">
       <c r="B802" t="s">
         <v>803</v>
       </c>
@@ -14557,7 +14551,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="803" spans="1:3">
+    <row r="803" spans="2:3">
       <c r="B803" t="s">
         <v>804</v>
       </c>
@@ -14565,7 +14559,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="804" spans="1:3">
+    <row r="804" spans="2:3">
       <c r="B804" t="s">
         <v>805</v>
       </c>
@@ -14573,7 +14567,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="805" spans="1:3">
+    <row r="805" spans="2:3">
       <c r="B805" t="s">
         <v>806</v>
       </c>
@@ -14581,7 +14575,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="806" spans="1:3">
+    <row r="806" spans="2:3">
       <c r="B806" t="s">
         <v>807</v>
       </c>
@@ -14589,7 +14583,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="807" spans="1:3">
+    <row r="807" spans="2:3">
       <c r="B807" t="s">
         <v>808</v>
       </c>
@@ -14597,7 +14591,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="808" spans="1:3">
+    <row r="808" spans="2:3">
       <c r="B808" t="s">
         <v>809</v>
       </c>
@@ -14605,7 +14599,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="809" spans="1:3">
+    <row r="809" spans="2:3">
       <c r="B809" t="s">
         <v>810</v>
       </c>
@@ -14613,7 +14607,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="810" spans="1:3">
+    <row r="810" spans="2:3">
       <c r="B810" t="s">
         <v>811</v>
       </c>
@@ -14621,7 +14615,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="811" spans="1:3">
+    <row r="811" spans="2:3">
       <c r="B811" t="s">
         <v>812</v>
       </c>
@@ -14629,7 +14623,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="812" spans="1:3">
+    <row r="812" spans="2:3">
       <c r="B812" t="s">
         <v>813</v>
       </c>
@@ -14637,7 +14631,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="813" spans="1:3">
+    <row r="813" spans="2:3">
       <c r="B813" t="s">
         <v>814</v>
       </c>
@@ -14645,7 +14639,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="814" spans="1:3">
+    <row r="814" spans="2:3">
       <c r="B814" t="s">
         <v>815</v>
       </c>
@@ -14653,7 +14647,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="815" spans="1:3">
+    <row r="815" spans="2:3">
       <c r="B815" t="s">
         <v>816</v>
       </c>
@@ -14661,7 +14655,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="816" spans="1:3">
+    <row r="816" spans="2:3">
       <c r="B816" t="s">
         <v>817</v>
       </c>
@@ -14738,25 +14732,19 @@
       </c>
     </row>
     <row r="824" spans="1:3">
-      <c r="A824">
-        <v>397.46</v>
-      </c>
       <c r="B824" t="s">
         <v>825</v>
       </c>
       <c r="C824" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="825" spans="1:3">
-      <c r="A825">
-        <v>397.46</v>
-      </c>
       <c r="B825" t="s">
         <v>826</v>
       </c>
       <c r="C825" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="826" spans="1:3">
@@ -16050,7 +16038,7 @@
     </row>
     <row r="986" spans="1:3">
       <c r="A986">
-        <v>472.43</v>
+        <v>357</v>
       </c>
       <c r="B986" t="s">
         <v>987</v>
@@ -21736,7 +21724,7 @@
     </row>
     <row r="1678" spans="1:3">
       <c r="A1678">
-        <v>443.87</v>
+        <v>543.83</v>
       </c>
       <c r="B1678" t="s">
         <v>1679</v>
@@ -21747,7 +21735,7 @@
     </row>
     <row r="1679" spans="1:3">
       <c r="A1679">
-        <v>443.87</v>
+        <v>543.83</v>
       </c>
       <c r="B1679" t="s">
         <v>1680</v>
@@ -21972,7 +21960,7 @@
     </row>
     <row r="1706" spans="1:3">
       <c r="A1706">
-        <v>426.02</v>
+        <v>524.79</v>
       </c>
       <c r="B1706" t="s">
         <v>1707</v>
@@ -21983,7 +21971,7 @@
     </row>
     <row r="1707" spans="1:3">
       <c r="A1707">
-        <v>426.02</v>
+        <v>524.79</v>
       </c>
       <c r="B1707" t="s">
         <v>1708</v>
@@ -21994,7 +21982,7 @@
     </row>
     <row r="1708" spans="1:3">
       <c r="A1708">
-        <v>426.02</v>
+        <v>524.79</v>
       </c>
       <c r="B1708" t="s">
         <v>1709</v>
@@ -22005,7 +21993,7 @@
     </row>
     <row r="1709" spans="1:3">
       <c r="A1709">
-        <v>426.02</v>
+        <v>524.79</v>
       </c>
       <c r="B1709" t="s">
         <v>1710</v>
